--- a/Feedback_CSAT/output/feedback_csat_detalle_mayo_2026.xlsx
+++ b/Feedback_CSAT/output/feedback_csat_detalle_mayo_2026.xlsx
@@ -998,7 +998,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CXF01CUX03 Sí Pushes</t>
+          <t>CXF01CUX03 P2 Pushes</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1008,7 +1008,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CXF01CUX03 P2 Pushes</t>
+          <t>CXF01CUX03 Sí Pushes</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1028,7 +1028,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CXF01CUX03 No avisos Pushes</t>
+          <t>CXF01CUX03 No sé Pushes</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1038,7 +1038,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CXF01CUX03 No sé Pushes</t>
+          <t>CXF01CUX03 Muy conforme Pushes</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1048,7 +1048,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CXF01CUX03 Muy conforme Pushes</t>
+          <t>CXF01CUX03 No avisos Pushes</t>
         </is>
       </c>
       <c r="B58" t="n">
